--- a/artfynd/A 54568-2021 artfynd.xlsx
+++ b/artfynd/A 54568-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120845539</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>120845521</v>
       </c>
       <c r="B3" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120845543</v>
+        <v>120845529</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78246</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1000,7 +1000,7 @@
         <v>120845553</v>
       </c>
       <c r="B5" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120845529</v>
+        <v>120845543</v>
       </c>
       <c r="B6" t="n">
-        <v>78243</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 54568-2021 artfynd.xlsx
+++ b/artfynd/A 54568-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120845539</v>
+        <v>120845529</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -767,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120845521</v>
+        <v>120845543</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -891,42 +877,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120845529</v>
+        <v>120845539</v>
       </c>
       <c r="B4" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -978,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1000,12 +985,7 @@
         <v>120845553</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,112 +1085,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>120845543</v>
-      </c>
-      <c r="B6" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Luspiegielas, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>621467</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7285717</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54568-2021 artfynd.xlsx
+++ b/artfynd/A 54568-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120845529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120845543</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120845539</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,8 +1104,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120845553</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>